--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,8 +786,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122930867</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122930867</v>
+        <v>136143709</v>
       </c>
       <c r="B2" t="n">
-        <v>58114</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rörmyran, Orrböle, Vb</t>
+          <t>V Rörmyran, Fällfors, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>728038</v>
+        <v>728074</v>
       </c>
       <c r="R2" t="n">
-        <v>7104300</v>
+        <v>7104047</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,24 +765,551 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136143709</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136143711</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93035</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>V Rörmyran, Fällfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>728058</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7104119</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136143711</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136143710</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79444</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>V Rörmyran, Fällfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>728069</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7104081</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136143710</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122930867</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rörmyran, Orrböle, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>728038</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7104300</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/122930867</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136143714</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98156</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rörmyran, Orrböle NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>728022</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7104279</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136143714</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136143716</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100320</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rörmyran, Orrböle NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>728015</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7104305</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136143716</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93035</v>
+        <v>93036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100320</v>
+        <v>100321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136143709</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93036</v>
+        <v>93037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136143710</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100321</v>
+        <v>100322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136143709</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93037</v>
+        <v>93043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136143710</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100322</v>
+        <v>100328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136143709</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93043</v>
+        <v>93044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136143710</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100328</v>
+        <v>100329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136143709</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93044</v>
+        <v>93050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136143710</v>
       </c>
       <c r="B4" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100329</v>
+        <v>100340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136143709</v>
       </c>
       <c r="B2" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93050</v>
+        <v>93057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136143710</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100340</v>
+        <v>100353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93057</v>
+        <v>93058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100353</v>
+        <v>100354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136143709</v>
       </c>
       <c r="B2" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93058</v>
+        <v>93071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136143710</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100354</v>
+        <v>100367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24846-2025 artfynd.xlsx
+++ b/artfynd/A 24846-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136143709</v>
       </c>
       <c r="B2" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136143711</v>
       </c>
       <c r="B3" t="n">
-        <v>93071</v>
+        <v>93072</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136143710</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136143714</v>
       </c>
       <c r="B6" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>136143716</v>
       </c>
       <c r="B7" t="n">
-        <v>100367</v>
+        <v>100368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
